--- a/output/catalogo_global.xlsx
+++ b/output/catalogo_global.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F432"/>
+  <dimension ref="A1:F740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14252,6 +14252,9862 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>8.7Kimetsu no Yaiba: Hashira Geiko-hen</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kimetsu-no-yaiba-hashira-geiko-hen/</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/wD55C85rLI568fxlQUhlTADdwo3.jpg</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>0Solo Leveling2024</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/upando-sozinho/</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/zn7hOslLYG1U2m06jGJJln8Ry7t.jpg</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>8.592Kono Subarashii Sekai ni Shukufuku wo! 3</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kono-subarashii-sekai-ni-shukufuku-wo-3/</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mu4F6a4ImUT5xqYlc0IcwHaALKE.jpg</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>0Lv2 kara Cheat datta Motoyuusha Kouho no Mattari Isekai Life</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/lv2-kara-cheat-datta-motoyuusha-kouho-no-mattari-isekai-life/</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/uU8JO4PsbgpuZmbkUMPjdpxEjBO.jpg</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>8.4Bleach: Sennen Kessen-hen2023</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/bleach-sennen-kessen-hen/</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/guyS28A4IxwoMXIq3Xj9AszMefP.jpg</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>7.923Fog Hill of Five Elements 22023</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/fog-hill-of-five-elements-2/</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ad8ECFk6fFNmvJtwgzUoefiw5oL.jpg</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>44 Cut Hero2023</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/4-cut-hero/</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8Fjqbv0KWcm1yUhsqWAkkDCUVXm.jpg</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>8.544Jujutsu Kaisen2020</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/jujutsu-kaisen/</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/q3cKEEthevZvKRelF4Ko6cUnUdu.jpg</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>8.311Dorohedoro 2 Dublado</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dorohedoro-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/wLMh1Mm2uTVPK3MCPm8U9NK8JVD.jpg</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>10Isekai Nonbiri Nouka2023</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/isekai-nonbiri-nouka/</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mE4pE6NOV3AbvTUE3MkFMlfs12n.jpg</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>9Aishiteru Game wo Owarasetai2026</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/aishiteru-game-wo-owarasetai/</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/kK7T8DcXKWcYfR6Kvy0ouCBjMnU.jpg</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>8.5Ichijouma Mankitsugurashi!2026</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ichijouma-mankitsugurashi/</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/lMTqSZtz4Y6IBpxl6LklpwrxZ1.jpg</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>10Nippon Sangoku Dublado2026</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/nippon-sangoku-dublado/</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hjihUw4UPndUxklecJxz1qCbcjT.jpg</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>5.8Kuroneko to Majo no Kyoushitsu2026</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kuroneko-to-majo-no-kyoushitsu/</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/r7ec9R5MY39TPWDtj0SrqnDecsv.jpg</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>9.5Yowa Yowa Sensei2026</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yowa-yowa-sensei/</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/tHjbyrqvbBkF6XwZgdSn3o74WzK.jpg</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>10Hokuto no Ken: Fist of the North Star Dublado2026</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/hokuto-no-ken-fist-of-the-north-star-dublado/</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8SRwvqBl3yzhy6PwvZVXy1A14rd.jpg</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>10Hokuto no Ken: Fist of the North Star2026</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/hokuto-no-ken-fist-of-the-north-star/</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8SRwvqBl3yzhy6PwvZVXy1A14rd.jpg</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>6.5Kill Ao2026</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kill-ao/</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/i1RaaFQUSGfx48CavoBRqeloLYb.jpg</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>10Kamiina Botan, Yoeru Sugata wa Yuri no Hana2026</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kamiina-botan-yoeru-sugata-wa-yuri-no-hana/</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6qIzYYAMgFdlcHYy4IfJG3VuVlq.jpg</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>5.5Kami no Shizuku2026</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kami-no-shizuku/</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/eJngpqzGzppVkR5XoM9uuPFOukn.jpg</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>10Awajima Hyakkei2026</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/awajima-hyakkei/</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5mhq2ts5fRgLBh1F9yyiPp4ZRYQ.jpg</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>10Haibara-kun no Tsuyokute Seishun New Game2026</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/haibara-kun-no-tsuyokute-seishun-new-game/</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/3Bxl4kYXdGMMIoZXgDGzo26OiGH.jpg</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>10Kujima Utaeba Ie Hororo2026</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kujima-utaeba-ie-hororo/</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/agXbnHcwfL0kfh46mjaZbBxKlXQ.jpg</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>8.7Hime Kishi wa Barbaroi no Yome2026</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/hime-kishi-wa-barbaroi-no-yome/</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/aX6bcboTSrptEAnI3FaeEmpAHta.jpg</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>9.7Otaku ni Yasashii Gal wa Inai!?2026</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/otaku-ni-yasashii-gal-wa-inai/</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/bUZFEgXZFe26OhGqrsjGNrTxbmf.jpg</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>9Re:Zero kara Hajimeru Isekai Seikatsu 42026</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/rezero-kara-hajimeru-isekai-seikatsu-4/</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/x5UiAc6ry6uDMrT2FTJ75Y68WrV.jpg</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>10Kanojo, Okarishimasu 52026</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kanojo-okarishimasu-5/</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/lHt3j91jV7Kh6MuRJ4w8KmK3Xav.jpg</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>10Tadaima, Ojamasaremasu!2026</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tadaima-ojamasaremasu/</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ipc7ChnTAVAQWJm01UJFq3sjiOL.jpg</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>9.7Megami “Isekai Tensei Nani ni Naritai desu ka” Ore “Yuusha no Rokkotsu de”2026</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/megami-isekai-tensei-nani-ni-naritai-desu-ka-ore-yuusha-no-rokkotsu-de/</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/2cZEw2ntVk1lbcs1hqDjudKMzJr.jpg</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>9.1Isekai Nonbiri Nouka 22026</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/isekai-nonbiri-nouka-2/</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/dcD0mfG4qo5QJFpetkW6CkFb5JQ.jpg</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>7Hidarikiki no Eren2026</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/hidarikiki-no-eren/</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/v2ghoZFANzSNbH4ObmHrI9kVVdp.jpg</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>10Class de 2-banme ni Kawaii Onnanoko to Tomodachi ni Natta2026</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/class-de-2-banme-ni-kawaii-onnanoko-to-tomodachi-ni-natta/</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/smk2wgVAfdDDLr3NKW4uYlRoIWr.jpg</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>10Replica datte, Koi wo Suru.2026</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/replica-datte-koi-wo-suru/</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/rt3qJO775blT8zOj0vDknZG1aQt.jpg</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>9.9Marriagetoxin2026</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/marriagetoxin/</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/bHCm3vz7Mg60wEO6HTm9g2g8IEH.jpg</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>10Fullmetal Alchemist: Brotherhood Dublado2009</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/fullmetal-alchemist-brotherhood-dublado/</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/vIkH7fUQf8Olo8Apq56FQLGDXOo.jpg</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>8.5Liar Game2026</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/liar-game/</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/tGNeNhXzjNFJ6zaBqV3TKHtZpWy.jpg</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>9Tongari Boushi no Atelier Dublado2026</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tongari-boushi-no-atelier-dublado/</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1qGSBnrANHLX8C7KqGuPDCylns2.jpg</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>10Tongari Boushi no Atelier2026</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tongari-boushi-no-atelier/</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1qGSBnrANHLX8C7KqGuPDCylns2.jpg</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>9.3Ponkotsu Fuuki Iin to Skirt-take ga Futekisetsu na JK no Hanashi2026</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ponkotsu-fuuki-iin-to-skirt-take-ga-futekisetsu-na-jk-no-hanashi/</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/uBHcmbmC3TccLO6hdrttOpjy4bN.jpg</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>5Ghost Concert: Missing Songs2026</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ghost-concert-missing-songs/</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/yMt59KZr0OewyRs31Vd3zWuneeW.jpg</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>7Maid-san wa Taberu dake2026</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/maid-san-wa-taberu-dake/</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/3HYUZAeE1WrA9ATGv6GjeyL6mOO.jpg</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>8.9Tsue to Tsurugi no Wistoria 22026</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tsue-to-tsurugi-no-wistoria-2/</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1Pp08PmHpREp0uvMSu0ryCXpks1.jpg</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>9.5Nippon Sangoku2026</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/nippon-sangoku/</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hjihUw4UPndUxklecJxz1qCbcjT.jpg</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>8Mao2026</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mao/</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/kdti4Dm7XPV0Os2Jjzd188AWTQ3.jpg</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>6.3Needy Girl Overdose2026</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/needy-girl-overdose/</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/jl79CIc8yL0m5VKR2X1qkoAsre0.jpg</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>10Kami no Niwatsuki Kusunoki-tei2026</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kami-no-niwatsuki-kusunoki-tei/</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8WZ9Uhh7MJ3LQVGT6B84NysHNGQ.jpg</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>9.4Kanan-sama wa Akumade Choroi2026</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kanan-sama-wa-akumade-choroi/</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/xiPY3Rnak9CLenDjbiTsQWRwf8u.jpg</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>9.7Yomi no Tsugai Dublado2026</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yomi-no-tsugai-dublado/</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mNqW2jnAogZa0nJ94q1LUum8Hos.jpg</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>10Yomi no Tsugai2026</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yomi-no-tsugai/</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mNqW2jnAogZa0nJ94q1LUum8Hos.jpg</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>9.8Mairimashita! Iruma-kun 42026</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mairimashita-iruma-kun-4/</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5o1PjfSTASqjUH6giJXiskDbXpj.jpg</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>8.9Saikyou no Shokugyou wa Yuusha demo Kenja demo Naku Kanteishi (Kari) Rashii desu yo?2026</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/saikyou-no-shokugyou-wa-yuusha-demo-kenja-demo-naku-kanteishi-kari-rashii-desu-yo/</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/lHGyS1Ks0QdTtqw3aMjsdTbCC6T.jpg</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>10Honzuki no Gekokujou: Shisho ni Naru Tame ni wa Shudan wo Erandeiraremasen 42026</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/honzuki-no-gekokujou-shisho-ni-naru-tame-ni-wa-shudan-wo-erandeiraremasen-4/</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mbTWllleu9zYJqAIL8kZyvA1d5s.jpg</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>7.8Snowball Earth Dublado2026</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/snowball-earth-dublado/</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/61E9aXjYUGPfrO5CW2cTutu0jX3.jpg</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>7.7Snowball Earth2026</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/snowball-earth/</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/61E9aXjYUGPfrO5CW2cTutu0jX3.jpg</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>9.8Tensei shitara Slime Datta Ken 42026</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tensei-shitara-slime-datta-ken-4/</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/w59Rn0xX5BKTBJcV5sipzScxCAf.jpg</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>9.9Otonari no Tenshi-sama ni Itsunomanika Dame Ningen ni Sareteita Ken 22026</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/otonari-no-tenshi-sama-ni-itsunomanika-dame-ningen-ni-sareteita-ken-2/</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hXhtuSNOpOrLV734jPsTRhiuu2C.jpg</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>9.5Jishou Akuyaku Reijou na Konyakusha no Kansatsu Kiroku.2026</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/jishou-akuyaku-reijou-na-konyakusha-no-kansatsu-kiroku/</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ayhpfFHm1MtgPgLw3yN0euOUxsp.jpg</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>9.8Reincarnation no Kaben2026</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/reincarnation-no-kaben/</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ur7wRcNIO7ELC4YjZcvKRvxGCZc.jpg</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>7.6Mata Korosarete Shimatta no desu ne, Tantei-sama2026</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mata-korosarete-shimatta-no-desu-ne-tantei-sama/</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qiLz090XoM4MDkbNmRwNxtQdXZd.jpg</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>10Parede de Gelo Dublado2026</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/parede-de-gelo-dublado/</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/pIgAgsitVZPwDlijRC8zH8RuO69.jpg</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>8.3Koori no Jouheki2026</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/koori-no-jouheki/</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/lqUDZSU2DzorVDVS6dGgpiIh2ZK.jpg</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>9.5Fangkai Nage Nuwu2026</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/fangkai-nage-nuwu/</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/xoWmN0GRXtriUFMb8lJCyezQD5Y.jpg</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>9.3Nigashita Sakana wa Ookikatta ga Tsuriageta Sakana ga Ookisugita Ken2026</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/nigashita-sakana-wa-ookikatta-ga-tsuriageta-sakana-ga-ookisugita-ken/</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1D9htdBwuSQRL0jhoDty5TOSvBT.jpg</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>7.9Ganbare! Nakamura-kun!! Dublado2026</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ganbare-nakamura-kun-dublado/</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/rCI8bgsqoq2ho04ZE0gUr36l8Pg.jpg</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>8Ganbare! Nakamura-kun!!2026</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ganbare-nakamura-kun/</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/rCI8bgsqoq2ho04ZE0gUr36l8Pg.jpg</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>5.9Saikyou no Ousama, Nidome no Jinsei wa Nani wo Suru? 22026</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/saikyou-no-ousama-nidome-no-jinsei-wa-nani-wo-suru-2/</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/kD9617ZaR8rToD4G3TgsKOEs45N.jpg</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>9.5Jidou Hanbaiki ni Umarekawatta Ore wa Meikyuu wo Samayou 32026</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/jidou-hanbaiki-ni-umarekawatta-ore-wa-meikyuu-wo-samayou-3/</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/2F7zlgOtk9z0FGn2EjOFWDjGcBP.jpg</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>9.8Dorohedoro 22026</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dorohedoro-2/</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/wLMh1Mm2uTVPK3MCPm8U9NK8JVD.jpg</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>9.7Youkoso Jitsuryoku Shijou Shugi no Kyoushitsu e 42026</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/youkoso-jitsuryoku-shijou-shugi-no-kyoushitsu-e-4/</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6lNOqksJZAE4LzUs2yaqBpnZVm5.jpg</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>8.3Shunkashuutou Daikousha: Haru no Mai2026</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shunkashuutou-daikousha-haru-no-mai/</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hLyycun1uyo6TF0tbdEOF09yifr.jpg</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>10Soul Eater2008</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/soul-eater/</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hI5AhxFTSFabTG7Fvhczyb5ZIh8.jpg</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>9.7Soul Eater Dublado2008</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/soul-eater-dublado/</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qLROwgvaGIoogjD20a00uwJLi6t.jpg</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>7.2Invencível 42026</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/invencivel-4/</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qhb7RWU9ad9a5m3HbeRRXzjaMXf.jpg</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>9.2Steel Ball Run: JoJo no Kimyou na Bouken Dublado2026</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/steel-ball-run-jojo-no-kimyou-na-bouken-dublado/</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qP2klJJdlYpFNNS2a277JTkfauR.jpg</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>9.4Steel Ball Run: JoJo no Kimyou na Bouken2026</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/steel-ball-run-jojo-no-kimyou-na-bouken/</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qP2klJJdlYpFNNS2a277JTkfauR.jpg</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>10Niwatori Fighter2026</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/niwatori-fighter/</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/iCtbr0sIdaKZjhQH3Wr7hW6A1IU.jpg</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>9.5Niwatori Fighter Dublado2026</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/niwatori-fighter-dublado/</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/iCtbr0sIdaKZjhQH3Wr7hW6A1IU.jpg</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>9.1One Piece 2: A Série Dublado2026</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/one-piece-2-a-serie-dublado/</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/tvkBOJjbXDey64H6wIpX23yBnQ1.jpg</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>7.8Chapolin e Os Colorados Dublado2026</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/chapolin-e-os-colorados-dublado/</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hxb5sC1ZMXN4bEs1t6RKmLWhqt0.jpg</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>10Beastars 3 Final Season Part 22026</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/beastars-3-final-season-part-2/</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/89iCLAUPQmdfY8RXWjqmfVxqAwb.jpg</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>10Beastars 3 Final Season2024</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/beastars-3-final-season/</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/89iCLAUPQmdfY8RXWjqmfVxqAwb.jpg</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>8.4Beastars 22021</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/beastars-2/</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/68pGoBzmNZI3NXFIHH6Us9Eo3lA.jpg</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>10Beastars2019</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/beastars/</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/jJHykaBex66D01wlfPx0tcyEQ8E.jpg</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>9.7Carol e o Fim do Mundo Dublado2023</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/carol-e-o-fim-do-mundo-dublado/</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/pUHvR7n149Chmt6oMoLYUmWvpxh.jpg</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>10Festa da Salsicha: Comilândia 2 Dublado2024</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/festa-da-salsicha-comilandia-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/l8XFkTzWxObRLFqYlgZ1UBgvw5r.jpg</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>5Festa da Salsicha: Comilândia Dublado2024</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/festa-da-salsicha-comilandia-dublado/</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6kSblgQfbqDSo5gRIQ4vp706KTe.jpg</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>10As Tartarugas Ninjas 5 Dublado2012</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/as-tartarugas-ninjas-5-dublado/</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/jAoSfL20SHdaO0ptjg9sL3qxoFe.jpg</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>7As Tartarugas Ninjas 4 Dublado2012</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/as-tartarugas-ninjas-4-dublado/</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qWX6GJim140QS7Cp5whKD05sM8V.jpg</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>10As Tartarugas Ninjas 3 Dublado2012</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/as-tartarugas-ninjas-3-dublado/</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qgud4GJ9zCxiYj4Efjtgvc7fXcf.jpg</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>10As Tartarugas Ninjas 2 Dublado2012</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/as-tartarugas-ninjas-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7Gq8kAXzhgkYr3mQt1HG7N4GYv5.jpg</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>10As Tartarugas Ninjas Dublado2012</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/as-tartarugas-ninjas-dublado/</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/jAoSfL20SHdaO0ptjg9sL3qxoFe.jpg</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>10Baki-dou2026</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/baki-dou/</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qC4JawqYlUS9fwvAzGfY5lSz5uB.jpg</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>8.9BAKI-DOU: O Samurai Invencível Dublado2026</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/baki-dou-o-samurai-invencivel-dublado/</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gIuCoLJSD09qx16FUn2OckjL6CA.jpg</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>8Dragon Ball Z Legendado1989</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dragon-ball-z-legendado/</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/yfyToia25GnvjY7FPAGaCm3lKRc.jpg</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>9.4Dragon Ball Z Dublado1989</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dragon-ball-z-dublado/</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/f2zhRLqwRLrKhEMeIM7Z5buJFo3.jpg</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>8.8One Piece Dublado1999</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/one-piece-dublado/</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/wpVC1e0RVK2qRtZMFDYu1c6mHcy.jpg</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>10“Omae Gotoki ga Maou ni Kateru to Omouna” to Yuusha Party wo Tsuihou sareta node, Outo de Kimama ni Kurashitai Dublado</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/omae-gotoki-ga-maou-ni-kateru-to-omouna-to-yuusha-party-wo-tsuihou-sareta-node-outo-de-kimama-ni-kurashitai-dublado/</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/nH6Ch1q5rwdRs56bYTA9wuOhfbL.jpg</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>8.5Bleach Dublado2004</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/bleach-dublado/</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/e0kKmeM8R7Kersh5N2PPzIRNRhr.jpg</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>9.5Naruto Dublado2002</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/naruto-dublado/</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/9ptbVZpKNy5NY9D4zq4KGiYWRQY.jpg</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>9.3Naruto Shippuden Dublado2007</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/naruto-shippuden-dublado/</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/nRJmByfK9XdtOY73VArcN8KpKVs.jpg</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>10Sousou no Frieren 2 Dublado2026</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/sousou-no-frieren-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/cHhJzdUGcEBq6av4wr9jsIvUITH.jpg</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>9.4Jujutsu Kaisen Shimetsu Kaiyuu – Zenpen Dublado2026</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/jujutsu-kaisen-shimetsu-kaiyuu-zenpen-dublado/</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/dsbQuow3YDuhjIe2ig7R4Oivg96.jpg</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>8.2Digimon Frontier Dublado2002</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/digimon-frontier-dublado/</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hzlqEyPhDURcCXi4snIOdlLdZjo.jpg</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>10Neon Genesis Evangelion Dublado1995</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/neon-genesis-evangelion-dublado/</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/AhtWPHqIT1cWdrKTZVDMZD4Ca4F.jpg</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>10Neon Genesis Evangelion1995</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/neon-genesis-evangelion/</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/AhtWPHqIT1cWdrKTZVDMZD4Ca4F.jpg</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>9.3Koukyoushihen Eureka Seven2005</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/koukyoushihen-eureka-seven/</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/fbdM3vtY29PkipKrBb6NuTw7VDt.jpg</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>10Panty &amp; Stocking with Garterbelt2010</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/panty-stocking-with-garterbelt/</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/RPiVM7JIoAsOZEX0rW8tKQFvCR.jpg</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>10Digimon Savers Dublado2006</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/digimon-savers-dublado/</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mghmdyXQWJKETQEXx7er0PwVj5k.jpg</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>10Os Cavaleiros do Zodíaco: A Saga de Hades Dublado2002</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/os-cavaleiros-do-zodiaco-a-saga-de-hades-dublado/</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8nCfBKaGVftgH65FpKoGFIUNOob.jpg</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>9.6Os Cavaleiros do Zodíaco Dublado1986</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/os-cavaleiros-do-zodiaco-dublado/</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/e4cC6W5sSAKE8lQYRBTqU9jfdya.jpg</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>8Kui Cheng Shoufu Cong Youxi Kaishi2024</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kui-cheng-shoufu-cong-youxi-kaishi/</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/tSzLlfIDd4rXl8kakmvnaAtgDjh.jpg</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>10Medalist 2 Dublado2026</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/medalist-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7DXsDnyOTTlqcj1fKrNQz8Ftxco.jpg</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>9.5Medalist 22026</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/medalist-2/</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7DXsDnyOTTlqcj1fKrNQz8Ftxco.jpg</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>9.6Sousou no Frieren 22026</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/sousou-no-frieren-2/</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/cHhJzdUGcEBq6av4wr9jsIvUITH.jpg</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>9.6[Oshi no Ko] 32026</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/oshi-no-ko-3/</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/b9VpuTED5Z2JH3osUHYE85WtjaY.jpg</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>10Himesama “Goumon” no Jikan desu 22026</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/himesama-goumon-no-jikan-desu-2/</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/srOKrofia1ux6Y4DWmLHzJl25Ew.jpg</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>9.6Trigun Stargaze2026</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/trigun-stargaze/</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/nuIvj5os4aR32JyFaiLYBqFWPId.jpg</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>8.5Trigun Stampede2023</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/trigun-stampede/</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8mqvaj0a74JZkvCc4w1J2ePchl.jpg</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>10Marvel Anime: Homem de Ferro Dublado2010</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/marvel-anime-homem-de-ferro-dublado/</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/wlKrH2U6RT01z9CgJa5ZnOFcfeK.jpg</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>10Iron Man2010</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/iron-man/</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/wCZGFk4Jsrd3Cv7eM3gCdKbj6Bk.jpg</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>9.6Jigokuraku 22026</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/jigokuraku-2/</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/nanYJccQsftI3fLNkNYJ5zv2QTD.jpg</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>8.3Hikuidori: Ushuu Boro Tobi-gumi2026</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/hikuidori-ushuu-boro-tobi-gumi/</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/fHt1mLMViDFeFL3DULYbKIihkk3.jpg</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>8.5Akuyaku Reijou wa Ringoku no Outaishi ni Dekiai sareru2026</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/akuyaku-reijou-wa-ringoku-no-outaishi-ni-dekiai-sareru/</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/4ylPjOLYz11colsaiyF95JXk7SU.jpg</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>8.1Kaya-chan wa Kowakunai2026</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kaya-chan-wa-kowakunai/</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/jfWdGJ2HcaCMVRdOUBPd6ayYgz2.jpg</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>9.2Seihantai na Kimi to Boku Dublado2026</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/seihantai-na-kimi-to-boku-dublado/</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/xsqaVf4dtMYM9kcEgmtdDiTlkQl.jpg</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>9.8Seihantai na Kimi to Boku2026</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/seihantai-na-kimi-to-boku/</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/xsqaVf4dtMYM9kcEgmtdDiTlkQl.jpg</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>7.5Ganglion2025</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ganglion/</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5iR5HmBT8POUuGjKCrGA4mi6Z9U.jpg</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>9.8Uruwashi no Yoi no Tsuki2026</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/uruwashi-no-yoi-no-tsuki/</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/3061lEeTTSb5NtX0ASXnRSO7Mo5.jpg</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>8.7Yuusha no Kuzu2026</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yuusha-no-kuzu/</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/zUdByBz1zWn4Prgw5nkVmgfFzfI.jpg</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>10Jingai Kyoushitsu no Ningengirai Kyoushi2026</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/jingai-kyoushitsu-no-ningengirai-kyoushi/</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1GmD3pP3aCQAknNem6yaQ5gP5os.jpg</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>9.1Dead Account2026</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dead-account/</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7mdtTto2V1gTBYttzBd54ofE482.jpg</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>9.6Tensei shitara Dragon no Tamago datta2026</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tensei-shitara-dragon-no-tamago-datta/</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/bZwaRBpTiBDrNRA0SRcRE6Q0Ydd.jpg</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>8Android wa Keiken Ninzuu ni Hairimasu ka??2026</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/android-wa-keiken-ninzuu-ni-hairimasu-ka/</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/4dfyZ5UZKGuS5Pur5nMqFp6s675.jpg</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>9.5Hell Mode: Yarikomizuki no Gamer wa Hai Settei no Isekai de Musou suru2026</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/hell-mode-yarikomizuki-no-gamer-wa-hai-settei-no-isekai-de-musou-suru/</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/jTJWL2wKoukCaId1Tkd3NHDVSgw.jpg</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>8.7High School! Kimengumi2026</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/high-school-kimengumi/</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8ota15pVJEQYzEM0lVb9iVtUvPQ.jpg</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>8.6Dark Moon: Tsuki no Saidan Dublado2026</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dark-moon-tsuki-no-saidan-dublado/</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/3xMrv5JDbgy1AUj6GURBaTv8sNt.jpg</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>10Dark Moon: Tsuki no Saidan2026</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dark-moon-tsuki-no-saidan/</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/3xMrv5JDbgy1AUj6GURBaTv8sNt.jpg</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>10Jiisan Baasan Wakagaeru2024</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/jiisan-baasan-wakagaeru/</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8U1WYWvHUV796xbULylzvCuKffK.jpg</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>8.6Champignon no Majo2026</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/champignon-no-majo/</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gC4ZBJ4MsVNbhU595kyKGVwdNgP.jpg</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>5.5Shibou Yuugi de Meshi wo Kuu Dublado2026</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shibou-yuugi-de-meshi-wo-kuu-dublado/</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/oGuTKxRifOcbDb1VgEtRA6SEc6J.jpg</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>9.1“Omae Gotoki ga Maou ni Kateru to Omouna” to Yuusha Party wo Tsuihou sareta node, Outo de Kimama ni Kurashitai2026</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/omae-gotoki-ga-maou-ni-kateru-to-omouna-to-yuusha-party-wo-tsuihou-sareta-node-outo-de-kimama-ni-kurashitai/</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/nH6Ch1q5rwdRs56bYTA9wuOhfbL.jpg</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>7.4Odayaka Kizoku no Kyuuka no Susume2026</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/odayaka-kizoku-no-kyuuka-no-susume/</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/41ZzkDjfBnlDJPWpb4xWOIxrsH.jpg</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>10Eris no Seihai2026</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/eris-no-seihai/</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ifxEzlA8UWr1ZKHjYHKz59LzO9g.jpg</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>9.7Toumei Otoko to Ningen Onna: Sonouchi Fuufu ni Naru Futari2026</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/toumei-otoko-to-ningen-onna-sonouchi-fuufu-ni-naru-futari/</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/jU8Oc4XCKFNh2WxrDMXHQx6hfJy.jpg</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>9.8Mato Seihei no Slave 22026</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mato-seihei-no-slave-2/</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ieI3bn3oBKkqbJtYEPiaCV22Gps.jpg</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>10Douse, Koishite Shimaunda 22026</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/douse-koishite-shimaunda-2/</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qvfrC0SViT6LUOGNDxV2L8LcENs.jpg</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>9.4Jujutsu Kaisen Shimetsu Kaiyuu – Zenpen2026</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/jujutsu-kaisen-shimetsu-kaiyuu-zenpen/</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/zKFkzRn1UyE11Jv9CJjVmvmQFvR.jpg</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>5.7Shibou Yuugi de Meshi wo Kuu2026</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shibou-yuugi-de-meshi-wo-kuu/</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/oGuTKxRifOcbDb1VgEtRA6SEc6J.jpg</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>9.5Okiraku Ryoushu no Tanoshii Ryouchi Bouei2026</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/okiraku-ryoushu-no-tanoshii-ryouchi-bouei/</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/agP3f89RzO1We6Jb02QmbbSTeQ1.jpg</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>9.829-sai Dokushin Chuuken Boukensha no Nichijou2026</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/29-sai-dokushin-chuuken-boukensha-no-nichijou/</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/cqT49U15uBjkaR8n64rJ2Z9CkIP.jpg</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>6.6Arne no Jiken-bo2026</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/arne-no-jiken-bo/</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5RqIzLBLiMxD7KpYpnQP6TNsHOD.jpg</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>9.3O Incidente de Darwin Dublado2026</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/o-incidente-de-darwin/</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/sC2u3QLzFO0sruIQGNXw4Mo4Eqq.jpg</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>8.8Darwin Jihen2026</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/darwin-jihen/</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/yGtNkPSxeVaaORom5FgfBweIkSd.jpg</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>8.2Yoroi Shin Den Samurai Troopers2026</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yoroi-shin-den-samurai-troopers/</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gQDsN26g7RUibJJcgWzPvc0iTnb.jpg</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>8.1Yuusha Party ni Kawaii Ko ga Ita no de, Kokuhaku Shitemita2026</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yuusha-party-ni-kawaii-ko-ga-ita-no-de-kokuhaku-shitemita/</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/jjZG6tlLaih5twuv3H71GVDrgIu.jpg</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>8.8Mayonaka Heart Tune2026</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mayonaka-heart-tune/</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/otKyL6FiAoNAAB90N0cO3RhRhCj.jpg</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>7.4Isekai no Sata wa Shachiku Shidai2026</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/isekai-no-sata-wa-shachiku-shidai/</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/9ZtYwGcz9g6vcOBcFTMOFrYQVKs.jpg</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>10Maou no Musume wa Yasashi Sugiru!!2026</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/maou-no-musume-wa-yasashi-sugiru/</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gUpjTomq5J4aOpwAOJ3WB76kh5g.jpg</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>9.8Golden Kamuy: Saishuushou2026</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/golden-kamuy-saishuushou/</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/rVRpYvsyPgUUsuK0kQbya67ROPZ.jpg</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>8.5Osananajimi to wa Love Comedy ni Naranai2026</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/osananajimi-to-wa-love-comedy-ni-naranai/</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/rMoMsLOTbEKCWFEzgbxryoXUgRe.jpg</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>8.9Kirei ni Shitemoraemasu ka2026</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kirei-ni-shitemoraemasu-ka/</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/u3FoBE3Vw0tTHFV6djpSv5HHBU5.jpg</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>8.8Vigilante: Boku no Hero Academia ILLEGALS 2 Dublado2026</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/vigilante-boku-no-hero-academia-illegals-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/3INu3n1sUa9K3O5OTPrqvJOetbd.jpg</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>9.8Vigilante: Boku no Hero Academia ILLEGALS 22026</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/vigilante-boku-no-hero-academia-illegals-2/</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/3INu3n1sUa9K3O5OTPrqvJOetbd.jpg</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>6Saioshi no Gikei wo Mederu Tame, Nagaiki shimasu!2026</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/saioshi-no-gikei-wo-mederu-tame-nagaiki-shimasu/</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mvh4P253MjQ9T46hfTrMy1CN6B7.jpg</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>9.7Majutsushi Kunon wa Mieteiru2026</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/majutsushi-kunon-wa-mieteiru/</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/v05adzjtBOhTqu1Ri4FxOmu6Uix.jpg</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>8.5Hanazakari no Kimitachi e Dublado2026</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/hanazakari-no-kimitachi-e-dublado/</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/wCZn0Is62Tx4HC9WuFGYysjeHCx.jpg</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>10Hanazakari no Kimitachi e2026</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/hanazakari-no-kimitachi-e/</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/tetE5PpsRWUiXdElMdzchPuI3SQ.jpg</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>9.5Ikoku Nikki2026</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ikoku-nikki/</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/oMgxAEq7OVvkLDevVMfYwlAzBrP.jpg</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>10Goumon Baito-kun no Nichijou2026</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/goumon-baito-kun-no-nichijou/</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/o71krgHl9e4J7J6Rw6reqOXUAv3.jpg</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>9.5Kizoku Tensei: Megumareta Umare kara Saikyou no Chikara wo Eru2026</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kizoku-tensei-megumareta-umare-kara-saikyou-no-chikara-wo-eru/</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hNzGfrWuofXtorimdZMI1musY8H.jpg</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>10IDOLiSH7 Third Beat!2021</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/idolish7-third-beat/</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/cesDP0Cjzd6JTk884o7AdV7yIb4.jpg</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>7IDOLiSH7 Second Beat!2020</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/idolish7-second-beat/</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/nVyAVrk4sDIRrjHiZ0H3cOTvyNC.jpg</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>10IDOLiSH72018</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/idolish7/</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6SjRbdGaNQYBC47J0gprbq1vve1.jpg</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>10Natsume Yuujinchou Roku2017</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/natsume-yuujinchou-roku/</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/55T6xqnVBBB7MJuU7t5AkIoN7xe.jpg</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>8.1Natsume Yuujinchou Go2016</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/natsume-yuujinchou-go/</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gJwWgdV9Ir7CGqImEnLGaulKdpk.jpg</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>5.5Natsume Yuujinchou Shi2012</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/natsume-yuujinchou-shi/</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7rsZl2avRuFm8pBPemlMRLLivVo.jpg</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>8.1Natsume Yuujinchou San2011</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/natsume-yuujinchou-san/</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/cBGXwYuNSFaMTL06h6jXzvEpvr4.jpg</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>8.1Zoku Natsume Yuujinchou2009</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/zoku-natsume-yuujinchou/</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5AYtTMIYozhOT6KxBfWdr8ZoJEY.jpg</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>10Natsume Yuujinchou2008</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/natsume-yuujinchou/</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/l7oRoRrEV1k75gr6vY9FP7hzFye.jpg</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>10Cool Doji Danshi2022</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/cool-doji-danshi/</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/2CnXuF3rxRCG1Et8vrPdAcPbvwd.jpg</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>5.1The iDOLM@STER Cinderella Girls2015</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-idolmster-cinderella-girls/</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/o1Z73WXPziv3JjVpwfPbtoOMFfi.jpg</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>5.556The iDOLM@STER Shiny Colors 22024</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-idolmster-shiny-colors-2/</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/iv6OX4zL4foYWIaFczHUqwlnLka.jpg</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>5.556The iDOLM@STER Shiny Colors2024</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-idolmster-shiny-colors/</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/plv79G8KMsN4U8keajQKva3aSCy.jpg</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>5.8The iDOLM@STER Million Live!2023</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-idolmster-million-live/</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/2QXWC8GdhyOOT6ILI7LUzrcuiPM.jpg</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>4The iDOLM@STER SideM2017</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-idolmster-sidem/</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/eHUpKGmwnnuurz7DbiywkNL87LX.jpg</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>10Heaven Official’s Blessing2020</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/heaven-officials-blessing/</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/aDNWhM6F9BSP688AIRs4h7JePtf.jpg</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>9.5You and Idol Precure ♪2025</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/you-and-idol-precure-%e2%99%aa/</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/fvmTTlKu2Q6q4pQMu62SZpQEiVT.jpg</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>10The Daily Life of the Immortal King 52025</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-daily-life-of-the-immortal-king-5/</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/AiUzqwU9Dom6rH1Kt6jRXXGDD7p.jpg</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>10The Daily Life of the Immortal King 32022</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-daily-life-of-the-immortal-king-3/</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/9PbAAMobzKM76csFwjPHivT6UCi.jpg</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>10The Daily Life of the Immortal King 22021</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-daily-life-of-the-immortal-king-2/</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/msOLq5iRAcWPkaO1yHvFF0omsN2.jpg</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>8.3The Daily Life of the Immortal King2020</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-daily-life-of-the-immortal-king/</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/kjLWLqre00bkZ8aPU3hlwScuZMO.jpg</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>10Monster Strike: Deadverse Reloaded2025</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/monster-strike-deadverse-reloaded/</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/cPmRxg9Ww0TUr9O89Nu3ZoldTZk.jpg</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>9.8Yuusha-kei ni Shosu: Choubatsu Yuusha 9004-tai Keimu Kiroku Dublado2026</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yuusha-kei-ni-shosu-choubatsu-yuusha-9004-tai-keimu-kiroku-dublado/</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/rt29J2vs0AIc3S9mxnKv88qnTiJ.jpg</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>9.4Yuusha-kei ni Shosu: Choubatsu Yuusha 9004-tai Keimu Kiroku2026</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yuusha-kei-ni-shosu-choubatsu-yuusha-9004-tai-keimu-kiroku/</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/rt29J2vs0AIc3S9mxnKv88qnTiJ.jpg</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>9Dorohedoro Dublado2020</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dorohedoro-dublado/</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/70GLEznYQqJUQEN7dailanotIXn.jpg</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>10Dorohedoro2020</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dorohedoro/</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/70GLEznYQqJUQEN7dailanotIXn.jpg</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>10O Mundo Maravilhosamente Estranho de Gumball2025</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/o-mundo-maravilhosamente-estranho-de-gumball/</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/m8o1yMAGHLJMjjOSIidZ2BwZ6aF.jpg</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>10Caverna do Dragão1983</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/caverna-do-dragao/</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/4fFRnZwlOwhcZkwLK8DCxtApyYP.jpg</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>9.5MF Ghost 32026</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mf-ghost-3/</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/vMnd8iqPwOOoIZ9a2RcqAHppDoq.jpg</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>9.2Tamon-kun Ima Docchi!?2026</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tamon-kun-ima-docchi/</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1iTCxEIK1xlmIXjHcLjt0UyOU8w.jpg</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>9.3Yuusha Party wo Oidasareta Kiyoubinbou2026</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yuusha-party-wo-oidasareta-kiyoubinbou/</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/vdTDfjZkuzYFC1Xwa02kYvy41ET.jpg</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>10Isekai no Seikishi Monogatari2009</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/isekai-no-seikishi-monogatari/</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/tWq0Nbtq0ZbGSEyOwbOwNzycpNa.jpg</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>9.5Shigatsu wa Kimi no Uso2014</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shigatsu-wa-kimi-no-uso/</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/xswPti7YWJfvqFf52P5VAN1QMuJ.jpg</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>103-gatsu no Lion 22017</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/3-gatsu-no-lion-2/</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/zC4QhC2RlrwFLy4mBtgee7vZ8oR.jpg</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>103-gatsu no Lion2016</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/3-gatsu-no-lion/</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/4LTg5dLXnHwbNcFyOTnXvMpSs4q.jpg</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>10ReLIFE2016</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/relife/</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/oavCFoklxWAqPHSbuPaDZCZQ0gB.jpg</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>10NHK ni Youkoso!2006</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/nhk-ni-youkoso/</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5iXnyp9zQb3tNTSOXn0rAJOlxu0.jpg</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>10Rock wa Lady no Tashinami deshite2025</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/rock-wa-lady-no-tashinami-deshite/</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/c2Li4DhsSJiiKRpMHmTV462oSQH.jpg</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>10Ao no Miburo 22025</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ao-no-miburo-2/</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/aRWLrAXEVdcrF4bMpN1IdI5Yfo8.jpg</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>10Ooi! Tonbo 22024</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ooi-tonbo-2/</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/2J8hv7uhoDOW6CDJNCWjjo5tjln.jpg</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>10Super Choque Dublado2000</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/super-choque-dublado/</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/CAzxjYTUQoq2jeUnn0z6BugdIP.jpg</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>10Yu-Gi-Oh! Zero1998</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yu-gi-oh-zero/</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/dJ3aC5E8M7wSvzNOK72AvPxmS4C.jpg</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>9.5Ao no Orchestra 22025</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ao-no-orchestra-2/</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gQsieyi5yUN7Mrw4dSpiWjPSXbv.jpg</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>8.8One Punch Man 3 Dublado2025</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/one-punch-man-3-dublado/</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/a8BknzvFVK5EZ83rKg1a83iwaj0.jpg</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>7.2Pyramid Game2025</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/pyramid-game/</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/8as2sqZFWLRCB3ABO15rYHZUhzl.jpg</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>8.9Tatsuki Fujimoto 17-262025</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tatsuki-fujimoto-17-26/</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/zZW4CJQE7nfu8btJLoWIcOaa7fe.jpg</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>8.9Tatsuki Fujimoto 17-26 Dublado2025</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tatsuki-fujimoto-17-26-dublado/</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/zZW4CJQE7nfu8btJLoWIcOaa7fe.jpg</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>8.9Disney Twisted-Wonderland: A Série Dublado2025</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/disney-twisted-wonderland-a-serie-dublado/</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/c9RJoqZktpCQVUiZOhHLyq6Fhwb.jpg</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>6.2Disney Twisted-Wonderland The Animation2025</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/disney-twisted-wonderland-the-animation/</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/c9RJoqZktpCQVUiZOhHLyq6Fhwb.jpg</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>9.9Kekkon Yubiwa Monogatari 2 Dublado2025</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kekkon-yubiwa-monogatari-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/Ao0magelF5LRx1OIbgDdwXCoozf.jpg</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>8Toujima Tanzaburou wa Kamen Rider ni Naritai Dublado2025</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/toujima-tanzaburou-wa-kamen-rider-ni-naritai-dublado/</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/GBRHxhdyPb16pLDdKflPjvfWQg.jpg</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>8.5Boku no Hero Academia: Final Season Dublado2025</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/boku-no-hero-academia-final-season-dublado/</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1WgcPsaJZ2Dabs7YD1H5LxeeKIY.jpg</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>10Wandance Dublado2025</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/wandance-dublado/</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1FbU0jXGPTKKWtRkVD1zplH73La.jpg</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>10Ao no Exorcist 2 Dublado2017</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ao-no-exorcist-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qt1emEPDzc2x3q44AvedkPcXN3q.jpg</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>10Kimi to Koete Koi ni Naru2025</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kimi-to-koete-koi-ni-naru/</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/l8YQfVfTKtWnBS54cvHlCLeUidc.jpg</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>10Ranma ½ (2024) 2 Dublado2025</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ranma-%c2%bd-2024-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6vmdhryL8pOzXpHu293isC7uLwu.jpg</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>8.3Chanto Suenai Kyuuketsuki-chan2025</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/chanto-suenai-kyuuketsuki-chan/</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/4ldkUuEe5YqrJ6QwIxCFBSfv9wV.jpg</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>9.7Dragon Raja 2 (Dub Japonês)2025</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/dragon-raja-2-dub-japones/</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/4VLHu3LGgKJ6wcOtcbsYZJtWZr6.jpg</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.2Shinjiteita Nakamatachi ni Dungeon Okuchi de Korosarekaketa ga Gift “Mugen Gacha” de Level 9999 no Nakamatachi wo Te </t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shinjiteita-nakamatachi-ni-dungeon-okuchi-de-korosarekaketa-ga-gift-mugen-gacha-de-level-9999-no-nakamatachi-wo-te-ni-irete-moto-party-member-to-sekai-ni-fukushuu-zamaa-shimasu/</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/lFOtbsKfbrEixJXhHZLeoUtqUIn.jpg</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>6.1One Punch Man 32025</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/one-punch-man-3/</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/a8BknzvFVK5EZ83rKg1a83iwaj0.jpg</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>9.3Gnosia2025</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/gnosia/</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/2D4j3VlE2ZzNroic5imNLBQXGi.jpg</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>9.7Ninja to Gokudou Dublado2025</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ninja-to-gokudou-dublado/</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/37eik5Xi5xMjAzfkDaTO3Nc9nIT.jpg</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>9.7Sanda Dublado2025</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/sanda-dublado/</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5Nfdb0I8Az6rwSOtS4K0HnsHEd4.jpg</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>8Tensei Akujo no Kuro Rekishi2025</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tensei-akujo-no-kuro-rekishi/</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mPxqrX1cSrG63rFiCgGhYeG3PWX.jpg</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>9.1Wandance2025</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/wandance/</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1FbU0jXGPTKKWtRkVD1zplH73La.jpg</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>10Egao no Taenai Shokuba desu2025</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/egao-no-taenai-shokuba-desu/</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gVKAdE5KkozLw1MJDO10mrFnls2.jpg</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>9.5Ninja to Gokudou2025</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ninja-to-gokudou/</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/37eik5Xi5xMjAzfkDaTO3Nc9nIT.jpg</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>9.4Tondemo Skill de Isekai Hourou Meshi 22025</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tondemo-skill-de-isekai-hourou-meshi-2/</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6IZkTbgZEkzeVPKqfe644mSxbfF.jpg</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>8.4Chitose-kun wa Ramune Bin no Naka2025</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/chitose-kun-wa-ramune-bin-no-naka/</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mwR2mUXNpQaHxlL5iHXtKlSMfyY.jpg</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>8.9Ansatsusha de Aru Ore no Status ga Yuusha yori mo Akiraka ni Tsuyoi no da ga2025</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ansatsusha-de-aru-ore-no-status-ga-yuusha-yori-mo-akiraka-ni-tsuyoi-no-da-ga/</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/85YJUtguAWz2mJErJGUI55v26kw.jpg</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>103-nen Z-gumi Ginpachi-sensei2025</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/3-nen-z-gumi-ginpachi-sensei/</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/slneGllMqljglPzNVNoiiGPZp2J.jpg</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>10Debu to Love to Ayamachi to!2025</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/debu-to-love-to-ayamachi-to/</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/grkZwD5fHb3uHrzTn5mtXAq5Jl9.jpg</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>9.3Sawaranaide Kotesashi-kun2025</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/sawaranaide-kotesashi-kun/</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1p5uu6ukvj6CbWYQB1NEZr3TMr0.jpg</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>8.8Chichi wa Eiyuu Haha wa Seirei Musume no Watashi wa Tenseisha2025</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/chichi-wa-eiyuu-haha-wa-seirei-musume-no-watashi-wa-tenseisha/</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/i7sR7NbxWNlCkBHjoxcUfe3muLc.jpg</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>6.8Alma-chan wa Kazoku ni Naritai2025</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/alma-chan-wa-kazoku-ni-naritai/</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/784bVMnix50v3f4Aqn5bQqBRgoq.jpg</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>8.8Kikaijikake no Marie2025</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kikaijikake-no-marie/</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/tv8Vvu1pp3WkBu0g8kynX7zNH6y.jpg</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>9.5Digimon Beatbreak2025</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/digimon-beatbreak/</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/yV5O0AlpfAKOibDAzCQ6Gp7G6BU.jpg</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>4.6SI-VIS: The Sound of Heroes2025</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/si-vis-the-sound-of-heroes/</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/kFFQu047m2HGGlxcm4kAgqXt7j1.jpg</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>10Kingdom 62025</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kingdom-6/</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/c0kLtHi4K08asQkj48CWLxS3YY.jpg</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>9.2Nageki no Bourei wa Intai shitai 22025</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/nageki-no-bourei-wa-intai-shitai-2/</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/lQRskaix2xnMRx5MrnqQ4iLVN3E.jpg</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>8Tomodachi no Imouto ga Ore ni dake Uzai2025</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tomodachi-no-imouto-ga-ore-ni-dake-uzai/</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/HVmGFN9CmJCAKOGZoa99rLbE3h.jpg</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>9Fumetsu no Anata e 32025</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/fumetsu-no-anata-e-3/</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/2IIJ9sGdqhXs9k1PvznWbBmPaCY.jpg</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>10Ranma ½ (2024) 22025</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/ranma-%c2%bd-2024-2/</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6Qs9z2MEURhKtFUNh9U8AKbdeY2.jpg</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>9.9Spy x Family 32025</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/spy-x-family-3/</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/k1lvoAKlHLrB0vlW3l6AZJMGlk4.jpg</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>8Toujima Tanzaburou wa Kamen Rider ni Naritai2025</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/toujima-tanzaburou-wa-kamen-rider-ni-naritai/</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/GBRHxhdyPb16pLDdKflPjvfWQg.jpg</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>8.4Mikata ga Yowasugite Hojo Mahou ni Tesshiteita Kyuutei Mahoushi, Tsuihou sarete Saikyou wo Mezashimasu2025</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mikata-ga-yowasugite-hojo-mahou-ni-tesshiteita-kyuutei-mahoushi-tsuihou-sarete-saikyou-wo-mezashimasu/</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qTlOvHUYW9GtLVImNH3MeCGBldq.jpg</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>10Shuumatsu Touring2025</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shuumatsu-touring/</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/tVeLF6cUEqzdzqcEyWEN151zaa4.jpg</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>9.1Kekkon Yubiwa Monogatari 22025</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kekkon-yubiwa-monogatari-2/</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/uFVZJ34pcv0Y2fz2ZST2S8VZKBg.jpg</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>9.5The Fated Magical Princess: Who Made Me a Princess (Dub Japonês)2025</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/the-fated-magical-princess-who-made-me-a-princess-dub-japones/</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mmrvO0JdjUdKzu9fVhzcen0KtrB.jpg</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>10Saigo ni Hitotsu dake Onegai Shite mo Yoroshii Deshou ka Dublado2025</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/saigo-ni-hitotsu-dake-onegai-shite-mo-yoroshii-deshou-ka-dublado/</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/mWD10mdFoXJFvHZR7VwAe7D1Q1r.jpg</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>8.1Kao ni Denai Kashiwada-san to Kao ni Deru Oota-kun2025</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kao-ni-denai-kashiwada-san-to-kao-ni-deru-oota-kun/</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gNPBdqx36IWhMLT3xrNDEpTcBl4.jpg</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>8.5Boku no Hero Academia: Final Season2025</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/boku-no-hero-academia-final-season/</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1WgcPsaJZ2Dabs7YD1H5LxeeKIY.jpg</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>9.1Saigo ni Hitotsu dake Onegai Shite mo Yoroshii Deshou ka2025</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/saigo-ni-hitotsu-dake-onegai-shite-mo-yoroshii-deshou-ka/</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7WVc8kFsHDKYp2U3tZgv3n9BCoG.jpg</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>7.2Sanda2025</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/sanda/</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5Nfdb0I8Az6rwSOtS4K0HnsHEd4.jpg</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>8.5Shabake2025</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shabake/</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/95frFI1k6Acjes3LNKAv4mexU0C.jpg</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>10Bukiyou na Senpai2025</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/bukiyou-na-senpai/</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/lGhX1PyfZp5WzQBUTQISeG2ae1S.jpg</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>9.2Akujiki Reijou to Kyouketsu Koushaku2025</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/akujiki-reijou-to-kyouketsu-koushaku/</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6E1hsfFlwWr14yxfgmt9Lt7Gjw9.jpg</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>7.6Watashi wo Tabetai, Hitodenashi2025</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/watashi-wo-tabetai-hitodenashi/</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/2FPfswdvih5tnseWAzgbiWb0JuR.jpg</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>9.2Taiyou yori mo Mabushii Hoshi2025</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/taiyou-yori-mo-mabushii-hoshi/</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hbzaM9SUYll3z408Q47OYj0ZHg8.jpg</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>8.2Kakuriyo no Yadomeshi 22025</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kakuriyo-no-yadomeshi-2/</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/iTKMY3oJtdGxK0zpZHTEkzQZwso.jpg</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>7.8Lets Play Quest-darake no My Life2025</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/lets-play-quest-darake-no-my-life/</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ohEVj2YPIyIJxuT9uw6r4eDMD5Q.jpg</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>9.9Yano-kun no Futsuu no Hibi2025</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yano-kun-no-futsuu-no-hibi/</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/xnSIm9IejX7g8sAsH0GidFlCIH4.jpg</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>8.7Sozai Saishuka no Isekai Ryokouki2025</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/sozai-saishuka-no-isekai-ryokouki/</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7uW8DjN1ukRd3GKIswzMVMpDDMh.jpg</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>9.2Yasei no Last Boss ga Arawareta!2025</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/yasei-no-last-boss-ga-arawareta/</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/uLkimDmIWb4VdgFUuiMlS8wGi5S.jpg</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>9.5Cat’s♥Eye (2025) Dublado2025</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/cats%e2%99%a5eye-2025-dublado/</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/pIHLz3KfZYdc4oGTw5AHHfo7pSb.jpg</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>9.7Cat’s♥Eye (2025)2025</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/cats%e2%99%a5eye-2025/</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/wg4LPYsGyEfQnCi9otmR41jRDRc.jpg</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>8.9Towa no Yuugure2025</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/towa-no-yuugure/</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qg8KcFJB5ySSEJv9OlMYK9JEMbV.jpg</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>8.5Mushoku no Eiyuu: Betsu ni Skill nanka Ira Nakattan Daga2025</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mushoku-no-eiyuu-betsu-ni-skill-nanka-ira-nakattan-daga/</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/o2axKodGsInHYbuGNk9uquENtfR.jpg</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>7.5Marvel Zumbis Dublado2025</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/marvel-zumbis-dublado/</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ifJayoMnxGF6Kgfn3xXfNcjtCrM.jpg</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>10Futurama Dublado1999</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/futurama/</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/6ZS8SOno6kTmWz4eQ8lX8EBXOMv.jpg</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>9.3Grand Blue 22025</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/grand-blue-2/</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qgB3NPnZl22YiXwXo2OIGgliM8v.jpg</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>9.9Grand Blue2018</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/grand-blue/</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/u9dghzuBEtMxlIyoXbPBZ6HfX6z.jpg</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>9.5Kaoru Hana wa Rin to Saku Dublado2025</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kaoru-hana-wa-rin-to-saku-dublado/</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/khxkciCkPVG1c7R00vNZFxqgqFE.jpg</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>10Shingeki no Kyojin 22017</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shingeki-no-kyojin-2/</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/glGW1FMvxqcFxvcAoJVYRyux2hW.jpg</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>9.8Super Cube Dublado2025</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/super-cube-dublado/</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/s1h6Iqzuce2yTbOL5gxAWQe9T6p.jpg</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>9Kaijuu 8-gou 2 Dublado2025</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kaijuu-8-gou-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/A6JOsCdFFTxtbDnKAfE0iY6jOiE.jpg</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>10Shin Samurai-den Yaiba Dublado2025</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/shin-samurai-den-yaiba-dublado/</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1jltcsz17CkfyhpcsSlmVC6pQGh.jpg</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>8.8Fermat no Ryouri2025</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/fermat-no-ryouri/</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/22T1A22tDMYG0SMEAiQqmCZrIQw.jpg</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>10Futari Solo Camp Dublado2025</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/futari-solo-camp-dublado/</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gP7rdhoejxIwZUzB6vpnlsQsdOB.jpg</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>9.2Tsuyokute New Saga Dublado2025</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tsuyokute-new-saga-dublado/</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7WAVcPVqdLK9whw75A7z6qeiuCg.jpg</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>8.7Sono Bisque Doll wa Koi wo Suru 2 Dublado2025</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/sono-bisque-doll-wa-koi-wo-suru-2-dublado/</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/j5tZc3bbdxLQic4TmFATwSkTIPa.jpg</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>9.3Karaoke Iko!2025</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/karaoke-iko/</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qQxZSf0bHv2DJcXidv4HGfyIt9s.jpg</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>9.5Lord Of Mysteries Dublado2025</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/lord-of-mysteries-dublado/</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/1uxYvWDU7jpc1sQSzb3WfX4nB8q.jpg</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>8.2Arknights: Enshin Shomei2025</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/arknights-enshin-shomei/</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/h0Z2mfwIVIPDb7g6Z1nd3zMBgs.jpg</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>7.7Arknights: Fuyukomori Kaerimichi2023</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/arknights-fuyukomori-kaerimichi/</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/7btGc8IrTyDFmzsBHlygy1Joz8J.jpg</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>10Arknights: Reimei Zensou2022</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/arknights-reimei-zensou/</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/qpcynq9iFLZX527Q7mhZT4XWwu5.jpg</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>8.3Long Zu 2: Daowangzhe Zhi Tong2025</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/long-zu-2-daowangzhe-zhi-tong/</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/i3p7TZ8nvjE2JG3fpOi0vvI0HoW.jpg</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>10Long Zu2022</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/long-zu/</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/4VLHu3LGgKJ6wcOtcbsYZJtWZr6.jpg</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>7.9Nukitashi the Animation2025</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/nukitashi-the-animation/</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/zlybZJXfu4IpPnWXhnRtobl9BgZ.jpg</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>9.3Kaijuu 8-gou 22025</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/kaijuu-8-gou-2/</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/A6JOsCdFFTxtbDnKAfE0iY6jOiE.jpg</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>9.9Tensei shitara Dainana Ouji Datta node, Kimama ni Majutsu wo Kiwamemasu 22025</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tensei-shitara-dainana-ouji-datta-node-kimama-ni-majutsu-wo-kiwamemasu-2/</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/5E25pt7Tntkl1OvHnFpwe5RWZex.jpg</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>10Bad Girl2025</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/bad-girl/</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/ovE3txsuLdvpIPWpG4WodlkWXGi.jpg</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>9.6Tougen Anki Dublado2025</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tougen-anki-dublado/</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/v4OlQo5vj9aXW8oqd7q6w4ine67.jpg</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>8.2Tougen Anki2025</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/tougen-anki/</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/v4OlQo5vj9aXW8oqd7q6w4ine67.jpg</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>9.2Futari Solo Camp2025</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/futari-solo-camp/</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/gP7rdhoejxIwZUzB6vpnlsQsdOB.jpg</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>8.6New PANTY &amp; STOCKING with GARTERBELT Dublado2025</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/new-panty-stocking-with-garterbelt-dublado/</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hCOYjAsPuZeJUH9iMSor7RhJBd6.jpg</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Dublado</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>8.4New PANTY &amp; STOCKING with GARTERBELT2025</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/new-panty-stocking-with-garterbelt/</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/hCOYjAsPuZeJUH9iMSor7RhJBd6.jpg</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>10Mikadono Sanshimai wa Angai, Choroi2025</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>https://topanimes.net/animes/mikadono-sanshimai-wa-angai-choroi/</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>https://image.tmdb.org/t/p/w185/m1V6c1x127niTfg3k0rLWPouDSn.jpg</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Legendado</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>TopAnimes</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
